--- a/static/data/exports/Retro_DL_AE_2020.xlsx
+++ b/static/data/exports/Retro_DL_AE_2020.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -13894,11 +13894,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>16432</v>
+        <v>16525</v>
       </c>
       <c r="E183" t="n">
         <v>139</v>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -18067,7 +18067,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20865,7 +20865,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -21227,7 +21227,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -21452,7 +21452,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -21677,7 +21677,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -22189,7 +22189,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -22339,7 +22339,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -22517,11 +22517,11 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1503131</v>
+        <v>1503130</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Rakesh Kumar Narang</t>
+          <t>Naveen Kumar</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Rakesh Kumar Narang</t>
+          <t>Naveen Kumar</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -22573,7 +22573,7 @@
         </is>
       </c>
       <c r="P300" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Q300" t="b">
         <v>0</v>
@@ -22592,11 +22592,11 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1503130</v>
+        <v>1503131</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Naveen Kumar</t>
+          <t>Rakesh Kumar Narang</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Naveen Kumar</t>
+          <t>Rakesh Kumar Narang</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -22648,7 +22648,7 @@
         </is>
       </c>
       <c r="P301" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Q301" t="b">
         <v>0</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -23888,7 +23888,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -23963,7 +23963,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -24113,7 +24113,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
@@ -24325,7 +24325,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -24850,7 +24850,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -24925,7 +24925,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -25512,7 +25512,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -25724,7 +25724,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -25949,7 +25949,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -26024,7 +26024,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -26099,7 +26099,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -26324,7 +26324,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -26399,7 +26399,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -26761,7 +26761,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -26986,7 +26986,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -27136,7 +27136,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -27211,7 +27211,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -27423,7 +27423,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -27498,7 +27498,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
@@ -27573,7 +27573,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -27648,7 +27648,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -27873,7 +27873,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -28023,7 +28023,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -28098,7 +28098,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -28235,7 +28235,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -28310,7 +28310,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -28385,7 +28385,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -28610,7 +28610,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -28685,7 +28685,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -28835,7 +28835,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -29047,7 +29047,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -29122,7 +29122,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -29197,7 +29197,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -29272,7 +29272,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -29347,7 +29347,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -29497,7 +29497,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -29572,7 +29572,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -29797,7 +29797,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -29872,7 +29872,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
@@ -30309,7 +30309,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -30384,7 +30384,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -30459,7 +30459,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -30609,7 +30609,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -30684,7 +30684,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
@@ -30759,7 +30759,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -30834,7 +30834,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -30909,7 +30909,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -31196,7 +31196,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -31271,7 +31271,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -31633,7 +31633,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -31708,7 +31708,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -31783,7 +31783,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -32008,7 +32008,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -32308,7 +32308,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -32336,20 +32336,20 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1503264</v>
+        <v>1503263</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>M U Dua</t>
+          <t>Meena Suryawanshi</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>AHNP</t>
+          <t>RPPRINAT</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>16442</v>
+        <v>16421</v>
       </c>
       <c r="E433" t="n">
         <v>24</v>
@@ -32373,26 +32373,26 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>M U Dua</t>
+          <t>Meena Suryawanshi</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>AHNP</t>
+          <t>RPPRINAT</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P433" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Q433" t="b">
         <v>0</v>
@@ -32411,20 +32411,20 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1503263</v>
+        <v>1503264</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Meena Suryawanshi</t>
+          <t>M U Dua</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>RPPRINAT</t>
+          <t>AHNP</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>16421</v>
+        <v>16442</v>
       </c>
       <c r="E434" t="n">
         <v>24</v>
@@ -32448,26 +32448,26 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>Meena Suryawanshi</t>
+          <t>M U Dua</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>RPPRINAT</t>
+          <t>AHNP</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P434" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q434" t="b">
         <v>0</v>
@@ -32533,7 +32533,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -32758,7 +32758,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -32983,7 +32983,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -33058,7 +33058,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -33133,7 +33133,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O443" t="inlineStr">
@@ -33161,20 +33161,20 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1503274</v>
+        <v>1503275</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Amit Sharma</t>
+          <t>Shiv Kumar</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>VIJAYBHA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>16445</v>
+        <v>16208</v>
       </c>
       <c r="E444" t="n">
         <v>9</v>
@@ -33198,17 +33198,17 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>Amit Sharma</t>
+          <t>Shiv Kumar</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>VIJAYBHA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -33217,7 +33217,7 @@
         </is>
       </c>
       <c r="P444" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q444" t="b">
         <v>0</v>
@@ -33236,20 +33236,20 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>1503275</v>
+        <v>1503274</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Shiv Kumar</t>
+          <t>Amit Sharma</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>VIJAYBHA</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>16208</v>
+        <v>16445</v>
       </c>
       <c r="E445" t="n">
         <v>9</v>
@@ -33273,17 +33273,17 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>Shiv Kumar</t>
+          <t>Amit Sharma</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>VIJAYBHA</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -33292,7 +33292,7 @@
         </is>
       </c>
       <c r="P445" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q445" t="b">
         <v>0</v>
@@ -33358,7 +33358,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -33433,7 +33433,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
@@ -33508,7 +33508,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -33645,7 +33645,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O450" t="inlineStr">
@@ -33720,7 +33720,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O451" t="inlineStr">
@@ -33795,7 +33795,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -33870,7 +33870,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -33945,7 +33945,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -34020,7 +34020,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -34232,7 +34232,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O458" t="inlineStr">
@@ -34307,7 +34307,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O459" t="inlineStr">
@@ -34382,7 +34382,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
@@ -34457,7 +34457,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -34669,7 +34669,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -34744,7 +34744,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -34819,7 +34819,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -34894,7 +34894,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O468" t="inlineStr">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -35331,7 +35331,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -35406,7 +35406,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
@@ -35481,7 +35481,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -35556,7 +35556,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -35768,7 +35768,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -35843,7 +35843,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -35918,7 +35918,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O481" t="inlineStr">
@@ -35993,7 +35993,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -36068,7 +36068,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -36205,7 +36205,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -36280,7 +36280,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -36355,7 +36355,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -36430,7 +36430,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -36505,7 +36505,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -36580,7 +36580,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -36655,7 +36655,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -36805,7 +36805,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -37891,7 +37891,7 @@
       </c>
       <c r="N508" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O508" t="inlineStr">
@@ -37966,7 +37966,7 @@
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O509" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="N510" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O510" t="inlineStr">
@@ -38116,7 +38116,7 @@
       </c>
       <c r="N511" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O511" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="N513" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O513" t="inlineStr">
@@ -38328,7 +38328,7 @@
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O514" t="inlineStr">
@@ -38403,7 +38403,7 @@
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O515" t="inlineStr">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O516" t="inlineStr">
@@ -38553,7 +38553,7 @@
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O517" t="inlineStr">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="N518" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O518" t="inlineStr">
@@ -38703,7 +38703,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O519" t="inlineStr">
@@ -38778,7 +38778,7 @@
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O520" t="inlineStr">
@@ -38915,7 +38915,7 @@
       </c>
       <c r="N522" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O522" t="inlineStr">
@@ -38990,7 +38990,7 @@
       </c>
       <c r="N523" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O523" t="inlineStr">
@@ -39065,7 +39065,7 @@
       </c>
       <c r="N524" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O524" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O525" t="inlineStr">
@@ -39215,7 +39215,7 @@
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O526" t="inlineStr">
@@ -39290,7 +39290,7 @@
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O527" t="inlineStr">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="N528" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O528" t="inlineStr">
@@ -39502,7 +39502,7 @@
       </c>
       <c r="N530" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O530" t="inlineStr">
@@ -39577,7 +39577,7 @@
       </c>
       <c r="N531" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O531" t="inlineStr">
@@ -39652,7 +39652,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
@@ -39727,7 +39727,7 @@
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O533" t="inlineStr">
@@ -39802,7 +39802,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -39877,7 +39877,7 @@
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O535" t="inlineStr">
@@ -39952,7 +39952,7 @@
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O536" t="inlineStr">
@@ -40089,7 +40089,7 @@
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O538" t="inlineStr">
@@ -40164,7 +40164,7 @@
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O539" t="inlineStr">
@@ -40239,7 +40239,7 @@
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O540" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O541" t="inlineStr">
@@ -40389,7 +40389,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O542" t="inlineStr">
@@ -40539,7 +40539,7 @@
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O544" t="inlineStr">
@@ -40614,7 +40614,7 @@
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O545" t="inlineStr">
@@ -40689,7 +40689,7 @@
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O546" t="inlineStr">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O547" t="inlineStr">
@@ -40863,11 +40863,11 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>16432</v>
+        <v>16525</v>
       </c>
       <c r="E549" t="n">
         <v>683</v>
@@ -40901,7 +40901,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O549" t="inlineStr">
@@ -40976,7 +40976,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O550" t="inlineStr">
@@ -41051,7 +41051,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O551" t="inlineStr">
@@ -41126,7 +41126,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O552" t="inlineStr">
@@ -41201,7 +41201,7 @@
       </c>
       <c r="N553" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O553" t="inlineStr">
@@ -41276,7 +41276,7 @@
       </c>
       <c r="N554" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O554" t="inlineStr">
@@ -41351,7 +41351,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O555" t="inlineStr">
@@ -41426,7 +41426,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O556" t="inlineStr">
@@ -41501,7 +41501,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O557" t="inlineStr">
@@ -41576,7 +41576,7 @@
       </c>
       <c r="N558" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O558" t="inlineStr">
@@ -41713,7 +41713,7 @@
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O560" t="inlineStr">
@@ -41788,7 +41788,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O561" t="inlineStr">
@@ -41863,7 +41863,7 @@
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O562" t="inlineStr">
@@ -41938,7 +41938,7 @@
       </c>
       <c r="N563" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O563" t="inlineStr">
@@ -42013,7 +42013,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O564" t="inlineStr">
@@ -42088,7 +42088,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O565" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O566" t="inlineStr">
@@ -42238,7 +42238,7 @@
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O567" t="inlineStr">
@@ -42313,7 +42313,7 @@
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O568" t="inlineStr">
@@ -42388,7 +42388,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O569" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O570" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O590" t="inlineStr">
@@ -44012,7 +44012,7 @@
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O591" t="inlineStr">
@@ -44087,7 +44087,7 @@
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O592" t="inlineStr">
@@ -44162,7 +44162,7 @@
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O593" t="inlineStr">
@@ -44299,7 +44299,7 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O595" t="inlineStr">
@@ -44374,7 +44374,7 @@
       </c>
       <c r="N596" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O596" t="inlineStr">
@@ -44449,7 +44449,7 @@
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
@@ -44524,7 +44524,7 @@
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
@@ -44599,7 +44599,7 @@
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
@@ -44674,7 +44674,7 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
@@ -44824,7 +44824,7 @@
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
@@ -44899,7 +44899,7 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
@@ -44974,7 +44974,7 @@
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
@@ -45049,7 +45049,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
@@ -45124,7 +45124,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
@@ -45261,7 +45261,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
@@ -45336,7 +45336,7 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
@@ -45411,7 +45411,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
@@ -45486,7 +45486,7 @@
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
@@ -45561,7 +45561,7 @@
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O612" t="inlineStr">
@@ -45636,7 +45636,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O614" t="inlineStr">
@@ -45786,7 +45786,7 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
@@ -45923,7 +45923,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
@@ -45998,7 +45998,7 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O618" t="inlineStr">
@@ -46073,7 +46073,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O619" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O620" t="inlineStr">
@@ -46223,7 +46223,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O621" t="inlineStr">
@@ -46373,7 +46373,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
@@ -46448,7 +46448,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O624" t="inlineStr">
@@ -46523,7 +46523,7 @@
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O625" t="inlineStr">
@@ -46660,7 +46660,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O627" t="inlineStr">
@@ -46735,7 +46735,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O628" t="inlineStr">
@@ -46810,7 +46810,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O629" t="inlineStr">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
@@ -46960,7 +46960,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
@@ -47035,7 +47035,7 @@
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
@@ -47110,7 +47110,7 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O633" t="inlineStr">
@@ -47322,7 +47322,7 @@
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O636" t="inlineStr">
@@ -47397,7 +47397,7 @@
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O637" t="inlineStr">
@@ -47472,7 +47472,7 @@
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
@@ -47547,7 +47547,7 @@
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O639" t="inlineStr">
@@ -47622,7 +47622,7 @@
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
@@ -47697,7 +47697,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
@@ -47772,7 +47772,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
@@ -47909,7 +47909,7 @@
       </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O644" t="inlineStr">
@@ -47984,7 +47984,7 @@
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
@@ -48059,7 +48059,7 @@
       </c>
       <c r="N646" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
@@ -48134,7 +48134,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
@@ -49021,7 +49021,7 @@
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O659" t="inlineStr">
@@ -49096,7 +49096,7 @@
       </c>
       <c r="N660" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
@@ -49171,7 +49171,7 @@
       </c>
       <c r="N661" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
@@ -49246,7 +49246,7 @@
       </c>
       <c r="N662" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
@@ -49383,7 +49383,7 @@
       </c>
       <c r="N664" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O664" t="inlineStr">
@@ -49533,7 +49533,7 @@
       </c>
       <c r="N666" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O666" t="inlineStr">
@@ -49608,7 +49608,7 @@
       </c>
       <c r="N667" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O667" t="inlineStr">
@@ -49683,7 +49683,7 @@
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
@@ -49758,7 +49758,7 @@
       </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O669" t="inlineStr">
@@ -49833,7 +49833,7 @@
       </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
@@ -49908,7 +49908,7 @@
       </c>
       <c r="N671" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O671" t="inlineStr">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
@@ -50120,7 +50120,7 @@
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
@@ -50195,7 +50195,7 @@
       </c>
       <c r="N675" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O675" t="inlineStr">
@@ -50270,7 +50270,7 @@
       </c>
       <c r="N676" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
@@ -50345,7 +50345,7 @@
       </c>
       <c r="N677" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O677" t="inlineStr">
@@ -50420,7 +50420,7 @@
       </c>
       <c r="N678" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O678" t="inlineStr">
@@ -50557,7 +50557,7 @@
       </c>
       <c r="N680" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
@@ -50782,7 +50782,7 @@
       </c>
       <c r="N683" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O683" t="inlineStr">
@@ -50857,7 +50857,7 @@
       </c>
       <c r="N684" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
@@ -50932,7 +50932,7 @@
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
@@ -51007,7 +51007,7 @@
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
@@ -51082,7 +51082,7 @@
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
@@ -51157,7 +51157,7 @@
       </c>
       <c r="N688" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
@@ -51232,7 +51232,7 @@
       </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
@@ -51594,7 +51594,7 @@
       </c>
       <c r="N694" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
@@ -51669,7 +51669,7 @@
       </c>
       <c r="N695" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
@@ -51744,7 +51744,7 @@
       </c>
       <c r="N696" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
@@ -51819,7 +51819,7 @@
       </c>
       <c r="N697" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
@@ -51894,7 +51894,7 @@
       </c>
       <c r="N698" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
@@ -51969,7 +51969,7 @@
       </c>
       <c r="N699" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O699" t="inlineStr">
@@ -52706,7 +52706,7 @@
       </c>
       <c r="N709" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
@@ -52781,7 +52781,7 @@
       </c>
       <c r="N710" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
@@ -52856,7 +52856,7 @@
       </c>
       <c r="N711" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
@@ -53068,7 +53068,7 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
@@ -53143,7 +53143,7 @@
       </c>
       <c r="N715" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
@@ -53218,7 +53218,7 @@
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
@@ -53293,7 +53293,7 @@
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
@@ -53368,7 +53368,7 @@
       </c>
       <c r="N718" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
@@ -53518,7 +53518,7 @@
       </c>
       <c r="N720" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
@@ -53593,7 +53593,7 @@
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
@@ -53668,7 +53668,7 @@
       </c>
       <c r="N722" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
@@ -53743,7 +53743,7 @@
       </c>
       <c r="N723" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
@@ -53818,7 +53818,7 @@
       </c>
       <c r="N724" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O724" t="inlineStr">
@@ -53893,7 +53893,7 @@
       </c>
       <c r="N725" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
@@ -53968,7 +53968,7 @@
       </c>
       <c r="N726" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
@@ -54043,7 +54043,7 @@
       </c>
       <c r="N727" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
@@ -54118,7 +54118,7 @@
       </c>
       <c r="N728" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
@@ -54155,11 +54155,11 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D729" t="n">
-        <v>16432</v>
+        <v>16525</v>
       </c>
       <c r="E729" t="n">
         <v>414</v>
@@ -54193,7 +54193,7 @@
       </c>
       <c r="N729" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O729" t="inlineStr">
@@ -54330,7 +54330,7 @@
       </c>
       <c r="N731" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O731" t="inlineStr">
@@ -54405,7 +54405,7 @@
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O732" t="inlineStr">
@@ -54480,7 +54480,7 @@
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O733" t="inlineStr">
@@ -54555,7 +54555,7 @@
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O734" t="inlineStr">
@@ -54630,7 +54630,7 @@
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
@@ -54705,7 +54705,7 @@
       </c>
       <c r="N736" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O736" t="inlineStr">
@@ -54780,7 +54780,7 @@
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="N738" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O738" t="inlineStr">
@@ -54930,7 +54930,7 @@
       </c>
       <c r="N739" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O739" t="inlineStr">
@@ -55005,7 +55005,7 @@
       </c>
       <c r="N740" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O740" t="inlineStr">
@@ -55080,7 +55080,7 @@
       </c>
       <c r="N741" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O741" t="inlineStr">
@@ -55155,7 +55155,7 @@
       </c>
       <c r="N742" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O742" t="inlineStr">
@@ -55230,7 +55230,7 @@
       </c>
       <c r="N743" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O743" t="inlineStr">
